--- a/data/trans_dic/P1413-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1413-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 16,37</t>
+          <t>8,69; 16,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,14</t>
+          <t>3,6; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,91</t>
+          <t>6,64; 13,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 14,04</t>
+          <t>7,56; 14,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 18,8</t>
+          <t>10,33; 18,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 27,58</t>
+          <t>16,8; 27,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,15; 24,59</t>
+          <t>15,17; 24,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 14,74</t>
+          <t>9,15; 14,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 16,06</t>
+          <t>10,28; 15,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 17,23</t>
+          <t>10,92; 17,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 17,65</t>
+          <t>11,83; 17,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 13,43</t>
+          <t>9,0; 13,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,33; 25,56</t>
+          <t>18,3; 25,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,13</t>
+          <t>3,72; 8,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,86</t>
+          <t>3,15; 6,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,26</t>
+          <t>11,4; 18,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,38; 37,86</t>
+          <t>28,84; 37,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 15,69</t>
+          <t>9,72; 15,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,86</t>
+          <t>4,87; 9,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 33,49</t>
+          <t>26,58; 33,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,89; 30,53</t>
+          <t>24,58; 30,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,02</t>
+          <t>7,2; 10,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,38</t>
+          <t>4,38; 7,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 25,4</t>
+          <t>20,08; 25,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,99</t>
+          <t>5,58; 11,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,64</t>
+          <t>4,94; 10,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,87</t>
+          <t>5,1; 10,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 23,97</t>
+          <t>15,87; 23,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,97; 18,18</t>
+          <t>10,76; 18,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 19,16</t>
+          <t>11,06; 18,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 19,58</t>
+          <t>11,32; 19,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,77; 32,72</t>
+          <t>25,15; 32,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 13,89</t>
+          <t>9,05; 14,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,87</t>
+          <t>8,9; 14,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,04</t>
+          <t>8,95; 14,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,45; 27,15</t>
+          <t>21,7; 27,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 23,45</t>
+          <t>15,21; 23,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,42</t>
+          <t>6,93; 13,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,31</t>
+          <t>5,36; 11,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,44</t>
+          <t>10,32; 18,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 16,95</t>
+          <t>10,5; 17,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 25,1</t>
+          <t>17,01; 25,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 22,43</t>
+          <t>14,39; 22,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 30,84</t>
+          <t>26,02; 34,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 19,15</t>
+          <t>13,71; 18,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 18,36</t>
+          <t>12,88; 18,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,26</t>
+          <t>10,88; 15,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 24,69</t>
+          <t>19,43; 25,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,73</t>
+          <t>3,29; 10,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 20,33</t>
+          <t>10,39; 20,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,21</t>
+          <t>5,78; 13,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 20,29</t>
+          <t>11,42; 19,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 18,94</t>
+          <t>9,88; 19,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 38,45</t>
+          <t>26,01; 38,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,77</t>
+          <t>9,83; 19,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 26,49</t>
+          <t>19,07; 26,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 13,57</t>
+          <t>6,91; 12,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 27,83</t>
+          <t>19,52; 28,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,03</t>
+          <t>8,97; 15,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 22,23</t>
+          <t>16,26; 21,9</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,58; 17,44</t>
+          <t>9,63; 17,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 18,27</t>
+          <t>9,74; 18,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,51</t>
+          <t>5,92; 13,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,57; 30,81</t>
+          <t>21,24; 29,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,99</t>
+          <t>11,12; 20,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 23,02</t>
+          <t>12,96; 22,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,89; 16,63</t>
+          <t>8,02; 16,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,76; 40,58</t>
+          <t>31,43; 40,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,61; 17,43</t>
+          <t>11,55; 17,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,81; 19,1</t>
+          <t>12,98; 19,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,33</t>
+          <t>7,83; 13,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,07; 34,44</t>
+          <t>27,62; 33,83</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,97</t>
+          <t>12,58; 18,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 13,41</t>
+          <t>8,34; 13,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,87</t>
+          <t>7,22; 12,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,69; 30,13</t>
+          <t>22,68; 29,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,53; 16,87</t>
+          <t>11,37; 16,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,74</t>
+          <t>17,44; 23,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,7; 19,26</t>
+          <t>13,67; 19,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42,26; 78,56</t>
+          <t>40,21; 46,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,61</t>
+          <t>12,51; 16,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,67; 17,87</t>
+          <t>13,6; 17,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,15; 15,18</t>
+          <t>11,13; 14,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,13; 64,5</t>
+          <t>32,85; 38,01</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,02</t>
+          <t>18,15; 24,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,59</t>
+          <t>6,35; 10,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,57</t>
+          <t>6,55; 10,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 19,08</t>
+          <t>15,2; 20,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,03; 27,32</t>
+          <t>20,85; 27,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,87</t>
+          <t>12,68; 17,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,3; 15,2</t>
+          <t>10,31; 15,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,06; 31,89</t>
+          <t>25,23; 30,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,25; 24,44</t>
+          <t>20,16; 24,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 13,42</t>
+          <t>10,24; 13,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,02; 12,14</t>
+          <t>9,07; 12,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 24,22</t>
+          <t>21,02; 24,92</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,99; 17,44</t>
+          <t>14,99; 17,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 10,08</t>
+          <t>7,95; 10,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,16</t>
+          <t>7,25; 9,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,36</t>
+          <t>17,22; 20,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,49</t>
+          <t>17,81; 20,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,53</t>
+          <t>16,87; 19,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,29</t>
+          <t>12,75; 15,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,44</t>
+          <t>29,32; 31,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,88; 18,67</t>
+          <t>16,78; 18,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,84; 14,52</t>
+          <t>12,83; 14,6</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,33; 11,87</t>
+          <t>10,4; 11,95</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,91; 34,86</t>
+          <t>23,85; 25,64</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>69489</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23733; 44680</t>
+          <t>23727; 44849</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10034; 26927</t>
+          <t>10609; 26711</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19740; 40856</t>
+          <t>19509; 41069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22791; 43713</t>
+          <t>24107; 45375</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26237; 49032</t>
+          <t>26952; 48473</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49651; 79223</t>
+          <t>48250; 79068</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43745; 71004</t>
+          <t>43807; 71663</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26572; 42698</t>
+          <t>28920; 45135</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55756; 85734</t>
+          <t>54882; 84717</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64377; 100272</t>
+          <t>63525; 99419</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67337; 102780</t>
+          <t>68882; 103313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53832; 80722</t>
+          <t>57171; 83376</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>80483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>155235</t>
+          <t>161982</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>231978</t>
+          <t>242465</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90360; 126006</t>
+          <t>90248; 126177</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18347; 41113</t>
+          <t>18818; 42036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15264; 34469</t>
+          <t>15826; 34278</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59459; 99648</t>
+          <t>60371; 98798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>148078; 190815</t>
+          <t>145359; 187509</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50989; 82194</t>
+          <t>50912; 81822</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25901; 51581</t>
+          <t>25495; 50581</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>137560; 172237</t>
+          <t>145056; 182073</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>248173; 304388</t>
+          <t>245066; 302843</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74191; 113429</t>
+          <t>74130; 112097</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45138; 75662</t>
+          <t>44879; 74067</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>205240; 262069</t>
+          <t>216007; 270559</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61146</t>
+          <t>61447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>99333</t>
+          <t>101679</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>160479</t>
+          <t>163126</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18127; 38228</t>
+          <t>17786; 38069</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15192; 34484</t>
+          <t>16015; 35539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16628; 34627</t>
+          <t>16256; 34798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49705; 75753</t>
+          <t>50155; 75250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36806; 60991</t>
+          <t>36098; 60678</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38374; 65326</t>
+          <t>37722; 64688</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37490; 65850</t>
+          <t>38068; 66683</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86483; 114231</t>
+          <t>89620; 115511</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59098; 90887</t>
+          <t>59215; 93292</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59308; 92258</t>
+          <t>59186; 94472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58108; 91914</t>
+          <t>58637; 92070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>142700; 180628</t>
+          <t>145911; 181630</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>125525</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>163006</t>
+          <t>177088</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56420; 84096</t>
+          <t>54543; 85145</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24729; 50174</t>
+          <t>25935; 50434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19444; 41857</t>
+          <t>19822; 42110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35659; 63897</t>
+          <t>38508; 67869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38017; 62977</t>
+          <t>38998; 64221</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66058; 97639</t>
+          <t>66158; 97392</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55463; 86884</t>
+          <t>55727; 86611</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68794; 146688</t>
+          <t>109802; 144244</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98794; 139847</t>
+          <t>100129; 138553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>97362; 140036</t>
+          <t>98281; 139268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83248; 123102</t>
+          <t>82395; 121116</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>119123; 194607</t>
+          <t>154518; 199358</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>81780</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6619; 19776</t>
+          <t>6694; 20341</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21920; 43219</t>
+          <t>22091; 43729</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12103; 30008</t>
+          <t>12205; 27803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20557; 36109</t>
+          <t>23384; 40907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18970; 39324</t>
+          <t>20522; 40918</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57714; 84436</t>
+          <t>57113; 84701</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21942; 43218</t>
+          <t>21493; 42279</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40004; 55176</t>
+          <t>43265; 59365</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30054; 55782</t>
+          <t>28383; 53353</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83723; 120291</t>
+          <t>84353; 121039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38459; 64605</t>
+          <t>38574; 65914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>64815; 85851</t>
+          <t>70198; 94537</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>69215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>93127</t>
+          <t>95248</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>163618</t>
+          <t>164462</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25952; 47227</t>
+          <t>26067; 47919</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26692; 50062</t>
+          <t>26688; 50312</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16723; 35548</t>
+          <t>15572; 35636</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58152; 83063</t>
+          <t>57494; 80509</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31479; 55602</t>
+          <t>30937; 55633</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37337; 64019</t>
+          <t>36049; 62769</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21542; 45433</t>
+          <t>21913; 43787</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>81426; 104038</t>
+          <t>82693; 106317</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63759; 95707</t>
+          <t>63412; 96719</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70742; 105453</t>
+          <t>71652; 107084</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41663; 71464</t>
+          <t>41977; 72131</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>147673; 181151</t>
+          <t>147433; 180562</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162765</t>
+          <t>187323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>484036</t>
+          <t>336913</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>646801</t>
+          <t>524236</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>76406; 110512</t>
+          <t>77358; 111009</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55349; 88910</t>
+          <t>55305; 87764</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47670; 77923</t>
+          <t>47390; 79184</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>140694; 186869</t>
+          <t>162189; 210981</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>73610; 107697</t>
+          <t>72567; 106533</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>120467; 164717</t>
+          <t>121031; 163817</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94713; 133170</t>
+          <t>94493; 132937</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>358518; 666591</t>
+          <t>309890; 360957</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>157882; 208188</t>
+          <t>156824; 206118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185439; 242407</t>
+          <t>184533; 241737</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150278; 204542</t>
+          <t>150035; 198531</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>501178; 947229</t>
+          <t>488107; 564852</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123725</t>
+          <t>140067</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>205586</t>
+          <t>233499</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>329311</t>
+          <t>373566</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132892; 178692</t>
+          <t>134974; 179443</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>49363; 82500</t>
+          <t>49467; 82202</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>51219; 82284</t>
+          <t>51003; 82949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56379; 177243</t>
+          <t>121278; 162298</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>164735; 214062</t>
+          <t>163389; 211633</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>105726; 146987</t>
+          <t>104340; 146611</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>85109; 125553</t>
+          <t>85184; 126863</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>186436; 228152</t>
+          <t>209580; 256333</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>309307; 373315</t>
+          <t>307975; 373073</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>165164; 214982</t>
+          <t>163950; 215893</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>144697; 194865</t>
+          <t>145503; 196386</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>204518; 398206</t>
+          <t>342280; 405802</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>602060</t>
+          <t>654276</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1233663</t>
+          <t>1141936</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1835724</t>
+          <t>1796212</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>491205; 571470</t>
+          <t>491274; 578124</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>278887; 345582</t>
+          <t>272492; 346774</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>246051; 310896</t>
+          <t>245974; 309842</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>465913; 668553</t>
+          <t>607107; 705157</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>602194; 692257</t>
+          <t>601826; 696772</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>602211; 694407</t>
+          <t>599804; 695235</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>453078; 541806</t>
+          <t>451864; 539195</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1069708; 1662016</t>
+          <t>1093870; 1190892</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1123590; 1242838</t>
+          <t>1116665; 1239970</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>896548; 1013551</t>
+          <t>895592; 1019284</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>716938; 823410</t>
+          <t>721383; 829037</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1629138; 2479075</t>
+          <t>1731327; 1860958</t>
         </is>
       </c>
     </row>
